--- a/outputs/brand_laneige_kr_by_name.xlsx
+++ b/outputs/brand_laneige_kr_by_name.xlsx
@@ -716,10 +716,10 @@
         <v>146.6</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -765,10 +765,10 @@
         <v>107.1</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>40.2</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -867,10 +867,10 @@
         <v>22.2</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="O5" t="inlineStr"/>
     </row>
@@ -914,10 +914,10 @@
         <v>22.2</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="O6" t="inlineStr"/>
     </row>
@@ -961,10 +961,10 @@
         <v>19.2</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="O7" t="inlineStr"/>
     </row>
@@ -1008,10 +1008,10 @@
         <v>14.5</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="O8" t="inlineStr"/>
     </row>
@@ -1058,7 +1058,7 @@
         <v>11</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
@@ -1147,10 +1147,10 @@
         <v>1.8</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1000</v>
+        <v>1069</v>
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
@@ -1192,10 +1192,10 @@
         <v>1.8</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1000</v>
+        <v>1069</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>895</v>
+        <v>957</v>
       </c>
       <c r="O13" t="inlineStr"/>
     </row>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>895</v>
+        <v>957</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>895</v>
+        <v>957</v>
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>895</v>
+        <v>957</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>895</v>
+        <v>957</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
